--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91039</v>
+        <v>91044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91051</v>
+        <v>91054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91054</v>
+        <v>91057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91057</v>
+        <v>91061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91061</v>
+        <v>91068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91068</v>
+        <v>91070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128820270</v>
       </c>
       <c r="B2" t="n">
-        <v>91070</v>
+        <v>91071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48289-2025 artfynd.xlsx
+++ b/artfynd/A 48289-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128820270</v>
+        <v>128777492</v>
       </c>
       <c r="B2" t="n">
-        <v>91071</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6039941</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långbrännberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506505</v>
+        <v>506639</v>
       </c>
       <c r="R2" t="n">
-        <v>6947836</v>
+        <v>6948180</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 120-140 årig tallskog med bitvis stavatallkaraktär på mager häll/lavmark. Medelstor, ljusgul, geléaktig konsistens, klibbig och föll lätt isär.</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,6 +769,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128820270</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långbrännberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506505</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6947836</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 120-140 årig tallskog med bitvis stavatallkaraktär på mager häll/lavmark. Medelstor, ljusgul, geléaktig konsistens, klibbig och föll lätt isär.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
